--- a/products/EC_FleaMarket_AI_Listing_Kit_v0.1.xlsx
+++ b/products/EC_FleaMarket_AI_Listing_Kit_v0.1.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R7e70974f2d67407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Intake" sheetId="2" r:id="R7e1df008a24a49cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buyer Anxiety Map" sheetId="3" r:id="Rdd0d9e86fc7d46d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listing Copy Builder" sheetId="4" r:id="R89b38fc8f5d84ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Checklist" sheetId="5" r:id="R01570858f3224caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="After Listing Tests" sheetId="6" r:id="Ra5d29a0447544421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" r:id="R3195268ab3ae4583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品情報入力" sheetId="2" r:id="R4fba99c0284e4b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="購入前の不安" sheetId="3" r:id="R775cb020362c466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出品文作成" sheetId="4" r:id="R8e7cf3d70ae14243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認リスト" sheetId="5" r:id="Ra1defa6fec0d485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出品後テスト" sheetId="6" r:id="R1795ca31697c4390"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,51 +255,58 @@
       </x:c>
       <x:c r="B1" s="7"/>
     </x:row>
-    <x:row r="2" ht="33" customHeight="1"/>
+    <x:row r="2" ht="33" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="33" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>商品説明をAIに丸投げせず、事実確認・購入前不安・禁止表現チェックまで含めて、出品文を安全に改善するためのテンプレートです。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1"/>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+    </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>Step 1</x:v>
+        <x:v>手順 1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Product Intakeに商品の事実だけを入力する</x:v>
+        <x:v>商品情報入力に商品の事実だけを入力する</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Step 2</x:v>
+        <x:v>手順 2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Buyer Anxiety Mapで購入前の不安を洗い出す</x:v>
+        <x:v>購入前の不安で購入前の不安を洗い出す</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Step 3</x:v>
+        <x:v>手順 3</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Listing Copy BuilderのプロンプトをAIに貼る</x:v>
+        <x:v>出品 文章 作成のプロンプトをAIに貼る</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>Step 4</x:v>
+        <x:v>手順 4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>QA Checklistで誇張、未確認情報、規約リスクを削る</x:v>
+        <x:v>確認リストで誇張、未確認情報、規約リスクを削る</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>Step 5</x:v>
+        <x:v>手順 5</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>After Listing Testsで出品後の改善を記録する</x:v>
+        <x:v>出品後テストで出品後の改善を記録する</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
@@ -342,381 +349,381 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Field</x:v>
+        <x:v>項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Value</x:v>
+        <x:v>入力欄</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Required</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>AI Can Infer?</x:v>
+        <x:v>AIが推測可?</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Human Must Verify?</x:v>
+        <x:v>人の確認必須?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Risk If Wrong</x:v>
+        <x:v>間違えた時のリスク</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>商品名</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str"/>
+      <x:c r="B2" s="6"/>
       <x:c r="C2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>ワイヤレスイヤホン ABC-100</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>検索に出ない/誤認</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str"/>
+      <x:c r="H2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>ブランド/メーカー</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str"/>
+      <x:c r="B3" s="6"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Example Audio</x:v>
+        <x:v>例 Audio</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>偽物・誤認リスク</x:v>
       </x:c>
-      <x:c r="H3" s="6" t="str"/>
+      <x:c r="H3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>型番</x:v>
       </x:c>
-      <x:c r="B4" s="6" t="str"/>
+      <x:c r="B4" s="6"/>
       <x:c r="C4" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>ABC-100</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>互換性ミス</x:v>
       </x:c>
-      <x:c r="H4" s="6" t="str"/>
+      <x:c r="H4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>カテゴリ</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str"/>
+      <x:c r="B5" s="6"/>
       <x:c r="C5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>家電 / オーディオ</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>購入者期待のズレ</x:v>
       </x:c>
-      <x:c r="H5" s="6" t="str"/>
+      <x:c r="H5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str"/>
+      <x:c r="B6" s="6"/>
       <x:c r="C6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>目立つ傷なし / 箱に擦れあり</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>返品・低評価</x:v>
       </x:c>
-      <x:c r="H6" s="6" t="str"/>
+      <x:c r="H6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>サイズ/寸法</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str"/>
+      <x:c r="B7" s="6"/>
       <x:c r="C7" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>幅20cm 高さ12cm</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>使えない</x:v>
       </x:c>
-      <x:c r="H7" s="6" t="str"/>
+      <x:c r="H7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>色</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str"/>
+      <x:c r="B8" s="6"/>
       <x:c r="C8" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
         <x:v>ブラック</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>誤配送扱い</x:v>
       </x:c>
-      <x:c r="H8" s="6" t="str"/>
+      <x:c r="H8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>付属品</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="str"/>
+      <x:c r="B9" s="6"/>
       <x:c r="C9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>本体、充電ケーブル、説明書</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>クレーム</x:v>
       </x:c>
-      <x:c r="H9" s="6" t="str"/>
+      <x:c r="H9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>購入時期/使用期間</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str"/>
+      <x:c r="B10" s="6"/>
       <x:c r="C10" s="6" t="str">
-        <x:v>If known</x:v>
+        <x:v>わかれば</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>2025年購入、週1回使用</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>信頼低下</x:v>
       </x:c>
-      <x:c r="H10" s="6" t="str"/>
+      <x:c r="H10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>動作確認</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str"/>
+      <x:c r="B11" s="6"/>
       <x:c r="C11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
         <x:v>充電・接続確認済み</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>返品</x:v>
       </x:c>
-      <x:c r="H11" s="6" t="str"/>
+      <x:c r="H11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>発送方法</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str"/>
+      <x:c r="B12" s="6"/>
       <x:c r="C12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>匿名配送、緩衝材あり</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>配送トラブル</x:v>
       </x:c>
-      <x:c r="H12" s="6" t="str"/>
+      <x:c r="H12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>価格</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str"/>
+      <x:c r="B13" s="6"/>
       <x:c r="C13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>4,980円</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>販売不可</x:v>
       </x:c>
-      <x:c r="H13" s="6" t="str"/>
+      <x:c r="H13" s="6"/>
     </x:row>
     <x:row r="14" ht="33" hidden="0" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>強み</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="str"/>
+      <x:c r="B14" s="6"/>
       <x:c r="C14" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>軽い、接続が簡単</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>誇張</x:v>
       </x:c>
-      <x:c r="H14" s="6" t="str"/>
+      <x:c r="H14" s="6"/>
     </x:row>
     <x:row r="15" ht="33" hidden="0" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>弱み/注意点</x:v>
       </x:c>
-      <x:c r="B15" s="6" t="str"/>
+      <x:c r="B15" s="6"/>
       <x:c r="C15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>箱に擦れあり</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>低評価</x:v>
       </x:c>
-      <x:c r="H15" s="6" t="str"/>
+      <x:c r="H15" s="6"/>
     </x:row>
     <x:row r="16" ht="33" hidden="0" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>想定購入者</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str"/>
+      <x:c r="B16" s="6"/>
       <x:c r="C16" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>通勤用に安く探している人</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
         <x:v>訴求ズレ</x:v>
       </x:c>
-      <x:c r="H16" s="6" t="str"/>
+      <x:c r="H16" s="6"/>
     </x:row>
     <x:row r="17" ht="33" hidden="0" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>競合との差</x:v>
       </x:c>
-      <x:c r="B17" s="6" t="str"/>
+      <x:c r="B17" s="6"/>
       <x:c r="C17" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
         <x:v>付属品がそろっている</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
         <x:v>誇張</x:v>
       </x:c>
-      <x:c r="H17" s="6" t="str"/>
+      <x:c r="H17" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -737,22 +744,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Buyer Anxiety</x:v>
+        <x:v>購入前の不安</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Question To Answer</x:v>
+        <x:v>答える質問</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Where To Mention</x:v>
+        <x:v>書く場所</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Good Phrase</x:v>
+        <x:v>よい表現</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Bad Phrase</x:v>
+        <x:v>悪い表現</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Evidence Needed</x:v>
+        <x:v>必要な根拠</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -972,77 +979,77 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Output</x:v>
+        <x:v>成果物</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Prompt / Template</x:v>
+        <x:v>プロンプト / テンプレート</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Generated Draft</x:v>
+        <x:v>生成下書き</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Human Edits</x:v>
+        <x:v>人の修正</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Title</x:v>
+        <x:v>タイトル</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
         <x:v>商品名、ブランド、状態、主要特徴から検索されやすいタイトルを5案作ってください。誇張や未確認情報は入れないでください。</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str"/>
-      <x:c r="D2" s="6" t="str"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Short Description</x:v>
+        <x:v>短文 説明</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Product Intakeの事実だけを使って、購入前の不安を減らす短い説明文を作ってください。弱みも正直に入れてください。</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str"/>
-      <x:c r="D3" s="6" t="str"/>
+        <x:v>商品情報入力の事実だけを使って、購入前の不安を減らす短い説明文を作ってください。弱みも正直に入れてください。</x:v>
+      </x:c>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>Full Description</x:v>
+        <x:v>詳細文 説明</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
         <x:v>商品の強み、状態、付属品、発送、注意点を見出しつきで整理してください。事実不明な点は質問として返してください。</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str"/>
-      <x:c r="D4" s="6" t="str"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>FAQ</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Buyer Anxiety Mapをもとに、購入者が聞きそうなFAQを5つ作ってください。断定できないことは公式確認を促してください。</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="str"/>
-      <x:c r="D5" s="6" t="str"/>
+        <x:v>購入前の不安をもとに、購入者が聞きそうなFAQを5つ作ってください。断定できないことは公式確認を促してください。</x:v>
+      </x:c>
+      <x:c r="C5" s="6"/>
+      <x:c r="D5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Photo Checklist</x:v>
+        <x:v>写真 確認リスト</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
         <x:v>この商品を出品するために撮るべき写真を、購入者の不安別にリスト化してください。</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str"/>
-      <x:c r="D6" s="6" t="str"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Revision Prompt</x:v>
+        <x:v>修正 プロンプト</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
         <x:v>次の出品文を、誇張を削り、事実確認が必要な箇所を[要確認]として残して改善してください。</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str"/>
-      <x:c r="D7" s="6" t="str"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1062,19 +1069,19 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Check</x:v>
+        <x:v>確認項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Why</x:v>
+        <x:v>理由</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Pass?</x:v>
+        <x:v>合格?</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Fix If No</x:v>
+        <x:v>NG時の修正</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Examples</x:v>
+        <x:v>例</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1084,7 +1091,7 @@
       <x:c r="B2" s="6" t="str">
         <x:v>返品や低評価を防ぐ</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str"/>
+      <x:c r="C2" s="6"/>
       <x:c r="D2" s="6" t="str">
         <x:v>効果表現を削る</x:v>
       </x:c>
@@ -1099,7 +1106,7 @@
       <x:c r="B3" s="6" t="str">
         <x:v>購入後ギャップを減らす</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str"/>
+      <x:c r="C3" s="6"/>
       <x:c r="D3" s="6" t="str">
         <x:v>傷、汚れ、箱状態を追加</x:v>
       </x:c>
@@ -1114,7 +1121,7 @@
       <x:c r="B4" s="6" t="str">
         <x:v>信頼を守る</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str"/>
+      <x:c r="C4" s="6"/>
       <x:c r="D4" s="6" t="str">
         <x:v>不足写真を追加</x:v>
       </x:c>
@@ -1129,7 +1136,7 @@
       <x:c r="B5" s="6" t="str">
         <x:v>クレーム防止</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="str"/>
+      <x:c r="C5" s="6"/>
       <x:c r="D5" s="6" t="str">
         <x:v>写真のものが全て、と明記</x:v>
       </x:c>
@@ -1144,7 +1151,7 @@
       <x:c r="B6" s="6" t="str">
         <x:v>不安を減らす</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str"/>
+      <x:c r="C6" s="6"/>
       <x:c r="D6" s="6" t="str">
         <x:v>梱包、発送日を追加</x:v>
       </x:c>
@@ -1159,7 +1166,7 @@
       <x:c r="B7" s="6" t="str">
         <x:v>購入判断を助ける</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str"/>
+      <x:c r="C7" s="6"/>
       <x:c r="D7" s="6" t="str">
         <x:v>買い替え等の理由を追加</x:v>
       </x:c>
@@ -1174,7 +1181,7 @@
       <x:c r="B8" s="6" t="str">
         <x:v>規約違反を避ける</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str"/>
+      <x:c r="C8" s="6"/>
       <x:c r="D8" s="6" t="str">
         <x:v>断定や医療的表現を削る</x:v>
       </x:c>
@@ -1189,7 +1196,7 @@
       <x:c r="B9" s="6" t="str">
         <x:v>誤購入防止</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str"/>
+      <x:c r="C9" s="6"/>
       <x:c r="D9" s="6" t="str">
         <x:v>公式仕様確認を促す</x:v>
       </x:c>
@@ -1204,7 +1211,7 @@
       <x:c r="B10" s="6" t="str">
         <x:v>信頼感を上げる</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str"/>
+      <x:c r="C10" s="6"/>
       <x:c r="D10" s="6" t="str">
         <x:v>短く具体化</x:v>
       </x:c>
@@ -1219,11 +1226,11 @@
       <x:c r="B11" s="6" t="str">
         <x:v>トラブル予防</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str"/>
+      <x:c r="C11" s="6"/>
       <x:c r="D11" s="6" t="str">
         <x:v>不明点は購入前に質問、と追加</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str"/>
+      <x:c r="E11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -1232,11 +1239,11 @@
       <x:c r="B12" s="6" t="str">
         <x:v>安全</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str"/>
+      <x:c r="C12" s="6"/>
       <x:c r="D12" s="6" t="str">
         <x:v>住所、名前、注文番号を削除</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str"/>
+      <x:c r="E12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -1245,11 +1252,11 @@
       <x:c r="B13" s="6" t="str">
         <x:v>停止防止</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str"/>
+      <x:c r="C13" s="6"/>
       <x:c r="D13" s="6" t="str">
         <x:v>プラットフォーム規約を確認</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str"/>
+      <x:c r="E13" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1272,113 +1279,113 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Date</x:v>
+        <x:v>日付</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Change</x:v>
+        <x:v>変更内容</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Before Views</x:v>
+        <x:v>変更前閲覧</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>After Views</x:v>
+        <x:v>変更後閲覧</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Likes / Saves</x:v>
+        <x:v>いいね/保存</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Questions</x:v>
+        <x:v>質問</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Sale?</x:v>
+        <x:v>売れた?</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Learning</x:v>
+        <x:v>学び</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
-      <x:c r="A2" s="6" t="str"/>
+      <x:c r="A2" s="6"/>
       <x:c r="B2" s="6" t="str">
         <x:v>タイトルに型番を追加</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str"/>
-      <x:c r="D2" s="6" t="str"/>
-      <x:c r="E2" s="6" t="str"/>
-      <x:c r="F2" s="6" t="str"/>
-      <x:c r="G2" s="6" t="str"/>
-      <x:c r="H2" s="6" t="str"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
-      <x:c r="A3" s="6" t="str"/>
+      <x:c r="A3" s="6"/>
       <x:c r="B3" s="6" t="str">
         <x:v>1枚目写真を変更</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str"/>
-      <x:c r="D3" s="6" t="str"/>
-      <x:c r="E3" s="6" t="str"/>
-      <x:c r="F3" s="6" t="str"/>
-      <x:c r="G3" s="6" t="str"/>
-      <x:c r="H3" s="6" t="str"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
-      <x:c r="A4" s="6" t="str"/>
+      <x:c r="A4" s="6"/>
       <x:c r="B4" s="6" t="str">
         <x:v>FAQを追加</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str"/>
-      <x:c r="D4" s="6" t="str"/>
-      <x:c r="E4" s="6" t="str"/>
-      <x:c r="F4" s="6" t="str"/>
-      <x:c r="G4" s="6" t="str"/>
-      <x:c r="H4" s="6" t="str"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
-      <x:c r="A5" s="6" t="str"/>
+      <x:c r="A5" s="6"/>
       <x:c r="B5" s="6" t="str">
         <x:v>傷の説明を具体化</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="str"/>
-      <x:c r="D5" s="6" t="str"/>
-      <x:c r="E5" s="6" t="str"/>
-      <x:c r="F5" s="6" t="str"/>
-      <x:c r="G5" s="6" t="str"/>
-      <x:c r="H5" s="6" t="str"/>
+      <x:c r="C5" s="6"/>
+      <x:c r="D5" s="6"/>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="6"/>
+      <x:c r="H5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str"/>
+      <x:c r="A6" s="6"/>
       <x:c r="B6" s="6" t="str">
         <x:v>発送条件を冒頭に移動</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str"/>
-      <x:c r="D6" s="6" t="str"/>
-      <x:c r="E6" s="6" t="str"/>
-      <x:c r="F6" s="6" t="str"/>
-      <x:c r="G6" s="6" t="str"/>
-      <x:c r="H6" s="6" t="str"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
-      <x:c r="A7" s="6" t="str"/>
+      <x:c r="A7" s="6"/>
       <x:c r="B7" s="6" t="str">
         <x:v>価格を5%調整</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str"/>
-      <x:c r="D7" s="6" t="str"/>
-      <x:c r="E7" s="6" t="str"/>
-      <x:c r="F7" s="6" t="str"/>
-      <x:c r="G7" s="6" t="str"/>
-      <x:c r="H7" s="6" t="str"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="6"/>
+      <x:c r="H7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
-      <x:c r="A8" s="6" t="str"/>
+      <x:c r="A8" s="6"/>
       <x:c r="B8" s="6" t="str">
         <x:v>購入者不安を1つ追記</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str"/>
-      <x:c r="D8" s="6" t="str"/>
-      <x:c r="E8" s="6" t="str"/>
-      <x:c r="F8" s="6" t="str"/>
-      <x:c r="G8" s="6" t="str"/>
-      <x:c r="H8" s="6" t="str"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6"/>
+      <x:c r="F8" s="6"/>
+      <x:c r="G8" s="6"/>
+      <x:c r="H8" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
